--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.01238</v>
+        <v>18.04706</v>
       </c>
       <c r="D2" t="n">
-        <v>17.32814</v>
+        <v>17.66516</v>
       </c>
       <c r="E2" t="n">
-        <v>17.63202</v>
+        <v>17.82082</v>
       </c>
       <c r="F2" t="n">
-        <v>44.98981</v>
+        <v>44.86484</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05436</v>
+        <v>0.05302</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92607</v>
+        <v>1.97274</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.32636</v>
+        <v>17.81109</v>
       </c>
       <c r="D3" t="n">
-        <v>17.54352</v>
+        <v>17.43671</v>
       </c>
       <c r="E3" t="n">
-        <v>17.78176</v>
+        <v>17.68872</v>
       </c>
       <c r="F3" t="n">
-        <v>45.47318</v>
+        <v>44.74729</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05261</v>
+        <v>0.05393</v>
       </c>
       <c r="H3" t="n">
-        <v>1.94978</v>
+        <v>1.92186</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.89152</v>
+        <v>17.85395</v>
       </c>
       <c r="D4" t="n">
-        <v>17.52488</v>
+        <v>17.53816</v>
       </c>
       <c r="E4" t="n">
-        <v>17.67321</v>
+        <v>17.58477</v>
       </c>
       <c r="F4" t="n">
-        <v>44.7729</v>
+        <v>45.63046</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05413</v>
+        <v>0.05255</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94436</v>
+        <v>1.95004</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.87866</v>
+        <v>17.67503</v>
       </c>
       <c r="D6" t="n">
-        <v>16.99631</v>
+        <v>17.23237</v>
       </c>
       <c r="E6" t="n">
-        <v>17.32377</v>
+        <v>17.55334</v>
       </c>
       <c r="F6" t="n">
-        <v>23.08122</v>
+        <v>22.90459</v>
       </c>
       <c r="G6" t="n">
-        <v>36.11975</v>
+        <v>36.5982</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.67748</v>
+        <v>17.68733</v>
       </c>
       <c r="D7" t="n">
-        <v>16.97846</v>
+        <v>16.84862</v>
       </c>
       <c r="E7" t="n">
-        <v>17.58922</v>
+        <v>17.47217</v>
       </c>
       <c r="F7" t="n">
-        <v>23.2942</v>
+        <v>22.94792</v>
       </c>
       <c r="G7" t="n">
-        <v>36.40499</v>
+        <v>36.68034</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.84052</v>
+        <v>17.69031</v>
       </c>
       <c r="D8" t="n">
-        <v>16.7704</v>
+        <v>16.86943</v>
       </c>
       <c r="E8" t="n">
-        <v>17.26312</v>
+        <v>17.42534</v>
       </c>
       <c r="F8" t="n">
-        <v>23.03648</v>
+        <v>22.85615</v>
       </c>
       <c r="G8" t="n">
-        <v>35.67973</v>
+        <v>36.21038</v>
       </c>
     </row>
   </sheetData>
